--- a/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
@@ -683,117 +683,117 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>h_01KZQYXT1FJA58BJT4J29BWW27</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQYXT1FJA58BJT4J29BWW27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RollOut Configurations</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>RollOut Configurations</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSHXF7Z0MW8W49X4TTD453F9</t>
+          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7Z0MW8W49X4TTD453F9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
     </row>

--- a/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,6 +988,28 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,29 +463,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisites</t>
+          <t>Key Functions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>h_01KW1HHNQKBTXW867P18733APR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KW1HHNQKBTXW867P18733APR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Integration Setup</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -495,41 +495,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J46AGRGRQPVRAPETC1V9F4Q4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Create Integration</t>
+          <t>Integration Setup</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J46B7Y1FJFZ9EF69E21925AA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Create Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -539,19 +539,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01KSEWCYK0E80GA55XQN2D4XX4</t>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWCYK0E80GA55XQN2D4XX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Overview</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,107 +561,107 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01KZQTV1P0XV20YR1VS76HKP8Q</t>
+          <t>h_01KSEWCYK0E80GA55XQN2D4XX4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQTV1P0XV20YR1VS76HKP8Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWCYK0E80GA55XQN2D4XX4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Select Source Application</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
+          <t>h_01KZQTV1P0XV20YR1VS76HKP8Q</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQTV1P0XV20YR1VS76HKP8Q</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Entra ID</t>
+          <t>Select Source Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KZQNM5GWNN9YMJ8RBZ11SBAC</t>
+          <t>h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQNM5GWNN9YMJ8RBZ11SBAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Entra ID</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
+          <t>h_01KZQNM5GWNN9YMJ8RBZ11SBAC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQNM5GWNN9YMJ8RBZ11SBAC</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KZQNQ8QWSVR6S7DEWSFMSRR4</t>
+          <t>h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQNQ8QWSVR6S7DEWSFMSRR4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Synchronization Settings</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,151 +671,151 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KSF8NGECRJN5RPS871WR2368</t>
+          <t>h_01KZQNQ8QWSVR6S7DEWSFMSRR4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSF8NGECRJN5RPS871WR2368</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQNQ8QWSVR6S7DEWSFMSRR4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Attribute Mapping</t>
+          <t>Data Synchronization Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KZQYXT1FJA58BJT4J29BWW27</t>
+          <t>h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQYXT1FJA58BJT4J29BWW27</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Operations</t>
+          <t>Attribute Mapping</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>h_01KZQYXT1FJA58BJT4J29BWW27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZQYXT1FJA58BJT4J29BWW27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RollOut Configurations</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>RollOut Configurations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Template Library</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,63 +913,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,54 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Select Source Application</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Application Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Application Settings</t>
+          <t>Target Application</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,29 +969,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KZTP8M66QEBVG4GGB0CSNZTM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZTP8M66QEBVG4GGB0CSNZTM</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,32 +1001,54 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/headings.xlsx
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KZTP8M66QEBVG4GGB0CSNZTM</t>
+          <t>h_01KZTPAJ54W7HAYPA57YRY8VM2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZTP8M66QEBVG4GGB0CSNZTM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Microsoft-Entra-Provisioning-Service-Integration-Guide/#h_01KZTPAJ54W7HAYPA57YRY8VM2</t>
         </is>
       </c>
     </row>
